--- a/results/Tabla7_metricas_globales.xlsx
+++ b/results/Tabla7_metricas_globales.xlsx
@@ -1,141 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabla7" sheetId="1" r:id="rId1"/>
-    <sheet name="Comparacion_pub_vs_D" sheetId="2" r:id="rId2"/>
-    <sheet name="Crudo_por_semilla" sheetId="3" r:id="rId3"/>
+    <sheet name="Tabla7" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Comparacion_pub_vs_D" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crudo_por_semilla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
-  <si>
-    <t>Roughness parameter</t>
-  </si>
-  <si>
-    <t>MAE [µm]</t>
-  </si>
-  <si>
-    <t>MSE [µm²]</t>
-  </si>
-  <si>
-    <t>RMSE [µm]</t>
-  </si>
-  <si>
-    <t>R²</t>
-  </si>
-  <si>
-    <t>Ra</t>
-  </si>
-  <si>
-    <t>Rz</t>
-  </si>
-  <si>
-    <t>0.495 ± 0.061</t>
-  </si>
-  <si>
-    <t>3.898 ± 0.326</t>
-  </si>
-  <si>
-    <t>0.416 ± 0.058</t>
-  </si>
-  <si>
-    <t>26.551 ± 1.298</t>
-  </si>
-  <si>
-    <t>0.644 ± 0.044</t>
-  </si>
-  <si>
-    <t>5.152 ± 0.125</t>
-  </si>
-  <si>
-    <t>0.864 ± 0.019</t>
-  </si>
-  <si>
-    <t>0.762 ± 0.012</t>
-  </si>
-  <si>
-    <t>param</t>
-  </si>
-  <si>
-    <t>metrica</t>
-  </si>
-  <si>
-    <t>D_12.2M</t>
-  </si>
-  <si>
-    <t>publicada</t>
-  </si>
-  <si>
-    <t>arquitectura</t>
-  </si>
-  <si>
-    <t>sd</t>
-  </si>
-  <si>
-    <t>delta</t>
-  </si>
-  <si>
-    <t>gana</t>
-  </si>
-  <si>
-    <t>dentro_de_1sd</t>
-  </si>
-  <si>
-    <t>MAE</t>
-  </si>
-  <si>
-    <t>MSE</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>seed</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>MAPE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -154,13 +49,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -448,577 +410,733 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Roughness parameter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MAE [µm]</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MSE [µm²]</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>RMSE [µm]</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.495 ± 0.061</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.416 ± 0.058</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.644 ± 0.044</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.864 ± 0.019</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3.898 ± 0.326</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>26.551 ± 1.298</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.152 ± 0.125</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.762 ± 0.012</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>metrica</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>D_12.2M</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publicada</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>arquitectura</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>gana</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dentro_de_1sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>0.428</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.4949</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0.0608</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.0669</v>
       </c>
-      <c r="H2" t="s">
-        <v>30</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>0.353</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>0.416</v>
       </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>0.0578</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>0.063</v>
       </c>
-      <c r="H3" t="s">
-        <v>30</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>0.594</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>0.6439</v>
       </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>0.0438</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.0499</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>0.885</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>0.864</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>0.0189</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>-0.021</v>
       </c>
-      <c r="H5" t="s">
-        <v>30</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>3.788</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>3.898</v>
       </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>0.3264</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>0.11</v>
       </c>
-      <c r="H6" t="s">
-        <v>30</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
       </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>26.969</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>26.5507</v>
       </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>1.2982</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>-0.4183</v>
       </c>
-      <c r="H7" t="s">
-        <v>29</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>5.193</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>5.1516</v>
       </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>0.1255</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>-0.0414</v>
       </c>
-      <c r="H8" t="s">
-        <v>29</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="I8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>0.758</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>0.7625</v>
       </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>0.0116</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>0.0045</v>
       </c>
-      <c r="H9" t="s">
-        <v>29</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="I9" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>10</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>190</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.8756224142437878</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0.4387667226752975</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>0.616762253511746</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0.3803956773568872</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>10.41185016381078</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>190</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>0.8780463960045376</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0.4638156644769701</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>0.6107226750208574</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>0.3729821857846319</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>11.50921331561116</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>190</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>0.8368292850460396</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0.578423474150252</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>0.7064278843043847</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.4990403557227692</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>15.30526206127195</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ra</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>190</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>0.8653956934669972</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.4985015820527906</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>0.6416175029424177</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>0.4116730200820634</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>12.8281915396035</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>190</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>0.7618309815434362</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>3.81880623944919</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>5.159812691658584</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>26.623667013001</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>12.49963299833256</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>11</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>190</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>0.7470730413275448</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>4.379520105727626</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>5.317271842376267</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>28.27337984572751</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>16.25562461065857</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>12</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>190</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>0.7748566470854648</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>3.713293418806245</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>5.016731614526121</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>25.16759609218586</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>12.43691010750832</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>13</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>190</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>0.7661751565423965</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>3.680542920992607</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>5.1125389431495</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>26.1380544452202</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>12.46094707813584</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>